--- a/list.xlsx
+++ b/list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16360" windowHeight="17010"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
   <si>
     <t>文章</t>
   </si>
@@ -106,6 +106,30 @@
     <t>评估了四种主流大模型（ChatGPT-3.5、ChatGPT-4、Bard AI和Bing Chat）在草酸盐膳食管理中的分类准确性，发现Bard AI以84%的总体准确率显著优于其他模型，而ChatGPT系列表现相对较差（52%和49%）</t>
   </si>
   <si>
+    <t>A Hybrid LLM based Model for Calorie Tracker and Dietary Control</t>
+  </si>
+  <si>
+    <t>ICEC</t>
+  </si>
+  <si>
+    <t>基于混合大语言模型（GPT-3/GPT-4）的卡路里追踪与饮食控制系统，通过集成文本描述、条形码扫描、图片识别与可穿戴设备数据，结合 LSTM/GRU 深度学习模块提供个性化营养建议与实时反馈，在 10-30 次测试中模型构建时间稳定在 1.3–3.2 秒、推理延迟低至 1.5 秒</t>
+  </si>
+  <si>
+    <t>Investigating GPT Models for Nutritional Accuracy:A Systematic Review and Performance Enhancement</t>
+  </si>
+  <si>
+    <t>毕业论文</t>
+  </si>
+  <si>
+    <t>针对 GPT 系列大模型的营养信息准确性系统研究，通过两阶段实验（首阶段评估 GPT-3.5/4 在 150 种食物上的营养估算误差，次阶段引入 NutritionIX API 的检索增强生成技术）将能量估算平均绝对误差降至 18.2 kcal（SMAPE 10.8%）</t>
+  </si>
+  <si>
+    <t>RoDE: Linear Rectified Mixture of Diverse Experts for Food Large Multi-Modal Models</t>
+  </si>
+  <si>
+    <t>基于线性整流混合专家（RoDE）架构的食品大模型多任务优化框架，通过异构 LoRA 专家池（秩 2/4/6/8）与 ReLU 稀疏路由机制，在 Uni-Food 数据集上实现食材识别 IoU 26.86%（较基线提升 18.9%）、食谱生成 SacreBLEU 9.66（提升 11.2%）及营养估算 pMAE 52.58（降低 1.0%）的全面性能突破</t>
+  </si>
+  <si>
     <t>Advancing Food Nutrition Estimation via Visual-Ingredient Feature Fusion</t>
   </si>
   <si>
@@ -215,6 +239,60 @@
   </si>
   <si>
     <t>在营养成分量化分析中，ChatGPT-4对能量的估算误差为36%，蛋白质28%，钾49%，磷54%，凸显其在精确营养计算中的系统性偏差</t>
+  </si>
+  <si>
+    <t>Prediction of Nutritional Content in Peruvian Lunch Meals by Large Language Models: A One-Shot Evaluation</t>
+  </si>
+  <si>
+    <t>针对秘鲁午餐营养评估的大模型性能研究，通过单样本提示策略测试 Gemma-3 系列模型（4B/12B/27B）对 510 道传统餐食的能量与微量营养素预测能力，发现 27B 模型在热量（MAE 108 kcal）、碳水化合物（MAE 26 g）及锌（MAE 1 mg）估算中误差最低，而 12B 模型在蛋白质预测上达成 70% 临床误差阈值符合率，揭示当前通用大模型在区域特色膳食营养量化任务中仍存在显著精度局限（平均符合率＜45%）</t>
+  </si>
+  <si>
+    <t>Artificial intelligence chatbots for the nutrition management of diabetes and the metabolic syndrome</t>
+  </si>
+  <si>
+    <t>EJCN</t>
+  </si>
+  <si>
+    <t>针对 ChatGPT（GPT-3.5-turbo）在糖尿病与代谢综合征营养管理中的性能评估研究，通过 63 个提示词系统测试其膳食干预、营养诊疗流程（NCP）及 1500 kcal 日菜单规划三大领域的输出准确性，发现尽管生成内容清晰度获评良好至优秀（3-4 分 Likert 量表），但在能量赤字建议（缺失率 100%）、体重管理（缺失率 85%）、微量营养素量化（钙与维生素 D 摄入量严重偏离推荐值）</t>
+  </si>
+  <si>
+    <t>Comparison of the Accuracy, Completeness, Reproducibility,and Consistency of Different AI Chatbots in ProvidingNutritional Advice: An Exploratory Study</t>
+  </si>
+  <si>
+    <t>JCM</t>
+  </si>
+  <si>
+    <t>针对 10 种通用大模型聊天机器人（含 ChatGPT-3.5/4.0、Gemini、Copilot 等）营养建议性能的探索性研究，通过连续三日提交肥胖无并发症（Case 1）及肥胖合并糖尿病、 sarcopenia 与慢性肾病（Case 2）的临床案例提示词，并由注册营养师从准确性、完整性、可复现性及一致性四维度评估输出结果，发现 ChatGPT-3.5 在基础案例中准确性最高（67.2%），但在复杂案例中所有模型均未达 50% 准确率，且普遍存在蛋白质建议自相矛盾（如同时推荐“增蛋白”与“限蛋白”）、能量计算偏差（最高达 55%）、及三日回答可复现率低下（ChatGPT-4.0 仅 50%）等严重缺陷</t>
+  </si>
+  <si>
+    <t>Knowledge-Infused LLM-Powered Conversational Health Agent: A Case Study for Diabetes Patients</t>
+  </si>
+  <si>
+    <t>EMBC</t>
+  </si>
+  <si>
+    <t>基于知识增强大语言模型（LLM）的对话健康代理（CHA），通过整合美国糖尿病协会（ADA）膳食指南与 Nutritionix 营养数据库，并嵌入营养摄入计算与风险评估分析工具，显著提升了对糖尿病患者日常饮食管理的精准性——在 100 例糖尿病相关膳食咨询测试中，其风险营养素（如碳水化合物、脂肪、蛋白质等）评估准确率全面超越 GPT-4（平均提升 35.7%），尤其在饱和脂肪（99% vs 68%）和蛋白质（90% vs 17%）判定上展现出色性能</t>
+  </si>
+  <si>
+    <t>From bytes to bites: application of large language models to enhance nutritional recommendations</t>
+  </si>
+  <si>
+    <t>CKJ</t>
+  </si>
+  <si>
+    <t>评估了大语言模型（LLMs）在慢性肾脏病（CKD）营养管理中的应用潜力与局限，指出当前模型（如 ChatGPT-4）在食谱生成与多语言翻译（Likert 评分 4/5）方面表现良好，但营养估算存在严重偏差：能量低估 36%、蛋白质低估 28%、电解质（钾、磷、钠）低估 49–54%，且图像识别辅助工具仅能识别 85% 可见成分</t>
+  </si>
+  <si>
+    <t>KERL: Knowledge-Enhanced Personalized Recipe Recommendation using Large Language Models</t>
+  </si>
+  <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>KERL——一种基于多 LoRA 适配器架构的知识增强大语言模型系统，通过整合 FoodKG（含 100 万食谱与 6700 万三元组）实现个性化食物推荐、食谱生成与营养分析的三元任务协同，其核心创新在于采用任务特异性 LoRA 微调（Phi-3-mini 为基础模型）与知识图谱子图检索增强技术，在自建的大规模基准测试（含 77,900 条约束性问答对）中显著超越基线模型：推荐模块 F1 达 85.4%（较 LLaMA-2 提升 56.5%），食谱生成 BLEU-4 提升至 0.347（较基准提升 20%），营养估算 MAE 降低 50%</t>
+  </si>
+  <si>
+    <t>构建 FoodNExTDB 专家标注食物图像数据库（含 9,263 张图像、50,000 个营养标签）系统评估六种前沿视觉-语言模型（VLMs），揭示闭源模型（Gemini/94.5% EWR、ChatGPT/90.7% EWR）在单产品图像识别中显著优于开源模型，但所有模型在细粒度烹饪风格识别上表现严重受限（最佳仅 50% EWR）</t>
   </si>
 </sst>
 </file>
@@ -227,7 +305,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +332,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Utopia-Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -721,133 +806,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -873,8 +958,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1187,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="165.272727272727" style="1" customWidth="1"/>
@@ -1239,7 +1324,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2">
@@ -1253,7 +1338,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="2">
@@ -1267,7 +1352,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="2">
@@ -1281,7 +1366,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="2">
@@ -1295,7 +1380,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="2">
@@ -1309,11 +1394,11 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>26</v>
@@ -1323,13 +1408,13 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C10" s="6" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D10" t="s">
@@ -1337,21 +1422,21 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="2">
@@ -1365,63 +1450,63 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="2">
         <v>2025</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>38</v>
+      <c r="A14" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="2">
         <v>2025</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="2">
         <v>2025</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>43</v>
+      <c r="A16" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="B16" s="2">
         <v>2025</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="2">
@@ -1435,80 +1520,217 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="2">
         <v>2025</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="2">
         <v>2025</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>53</v>
+      <c r="A20" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="B20" s="2">
         <v>2025</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>56</v>
+      <c r="A21" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="B21" s="2">
         <v>2025</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B22" s="2">
         <v>2025</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
         <v>60</v>
       </c>
-      <c r="D22" t="s">
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="6"/>
+      <c r="B23" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D29">
+  <sortState ref="A2:D27">
     <sortCondition ref="B2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="21600" windowHeight="9700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t>文章</t>
   </si>
@@ -49,7 +49,7 @@
     <t>IJCAI</t>
   </si>
   <si>
-    <t>AgriBERT的领域专用大语言模型，该模型通过在大型农业文本语料库上从头训练，并融合外部知识图谱进行微调，在食品描述与营养数据匹配的语义理解任务上显著优于通用大模型。</t>
+    <t>使用 AgriBERT（基于BERT架构并在农业语料上预训练的模型）结合 FoodOn 本体知识，解决了食品文本描述与营养数据库之间 语义匹配（Semantic Matching） 的准确性问题</t>
   </si>
   <si>
     <t>AI dietician: Unveiling the accuracy of ChatGPT’s nutritional estimations</t>
@@ -58,7 +58,7 @@
     <t>Nutrition</t>
   </si>
   <si>
-    <t>研究评估了ChatGPT在营养信息提供方面的准确性和可靠性，发现该大模型能够生成具有合理准确度的营养数据</t>
+    <t>评估了 ChatGPT，解决了在 膳食计划与体重管理 场景下，AI生成的能量及常量营养素（碳水、蛋白质、脂肪）数值与 USDA 标准数据相比的 准确性验证 问题</t>
   </si>
   <si>
     <t>AI-Powered Renal Diet Support: Performance of ChatGPT,Bard AI, and Bing Chat</t>
@@ -67,7 +67,7 @@
     <t>clinics and practice</t>
   </si>
   <si>
-    <t>评估了四种主流大语言模型（ChatGPT 3.5、ChatGPT 4、Bard AI和Bing Chat）在慢性肾脏病饮食管理中的分类准确性，发现ChatGPT 4在钾含量分类中表现最佳（准确率81%），而Bard AI在磷含量识别中达到完美准确率（100%）</t>
+    <t>对比了 ChatGPT、Bard AI 和 Bing Chat，解决了在 肾脏病（Renal Disease） 饮食管理中，准确分类食物中钾、磷、蛋白质等关键营养素含量以提供安全饮食建议的问题</t>
   </si>
   <si>
     <t>Consistency and Accuracy of Artificial Intelligence for Providing Nutritional Information</t>
@@ -76,7 +76,25 @@
     <t>JAMA</t>
   </si>
   <si>
-    <t>ChatGPT-3.5和ChatGPT-4在提供营养信息方面的一致性与准确性，发现虽然两种大模型在能量和宏量营养素估算方面与营养师推荐值无显著差异，但仅有35%-48%的食物项目能在±10%误差范围内达到准确，且ChatGPT-4存在蛋白质高估问题，表明当前大模型可作为实时营养分析工具，但尚不能替代专业营养师</t>
+    <t>评估了 AI 聊天机器人（主要指 ChatGPT），解决了在不同语言（英语和繁体中文）输入下，对222种食物项进行 能量与常量营养素估算 时的 一致性与准确性 问题</t>
+  </si>
+  <si>
+    <t>A Hybrid LLM based Model for Calorie Tracker and Dietary Control</t>
+  </si>
+  <si>
+    <t>ICEC</t>
+  </si>
+  <si>
+    <t>提出了一种混合模型，结合 BERT（用于食品分类）与 LSTM（用于序列预测），旨在解决卡路里追踪应用中 食品识别与热量估算 的效率与用户体验问题</t>
+  </si>
+  <si>
+    <t>Artificial intelligence chatbots for the nutrition management of diabetes and the metabolic syndrome</t>
+  </si>
+  <si>
+    <t>EJCN</t>
+  </si>
+  <si>
+    <t>评估了 ChatGPT，解决了为 2型糖尿病及代谢综合征 患者制定符合临床指南的膳食计划（包括菜单规划和特定营养素建议）的 依从性与质量 问题</t>
   </si>
   <si>
     <t>CaLoRAify: Calorie Estimation with Visual-Text Pairing and LoRA-Driven Visual Language Models</t>
@@ -85,7 +103,16 @@
     <t>pre</t>
   </si>
   <si>
-    <t>结合视觉-语言大模型（VLM）与低秩自适应（LoRA）和检索增强生成（RAG）技术，实现了仅需单张食物图像即可准确估算热量并分析营养成分的创新系统</t>
+    <t>提出了 CaLoRAify，利用 LLaVA 视觉语言模型结合 LoRA 微调 和视觉-文本配对策略，解决了基于图像的 卡路里估算 中因缺乏领域特定数据导致的准确性低的问题</t>
+  </si>
+  <si>
+    <t>Comparison of the Accuracy, Completeness, Reproducibility,and Consistency of Different AI Chatbots in ProvidingNutritional Advice: An Exploratory Study</t>
+  </si>
+  <si>
+    <t>JCM</t>
+  </si>
+  <si>
+    <t>该研究对比了 ChatGPT-3.5, ChatGPT-4, Copilot 和 Gemini，解决了在五种不同临床状况（如糖尿病、妊娠、肌肉减少症等）下提供 营养建议 的准确性、完整性及可重复性评估问题</t>
   </si>
   <si>
     <t>Dietary Assessment with Multimodal ChatGPT: A Systematic Analysis</t>
@@ -94,7 +121,25 @@
     <t xml:space="preserve">IEEE BHI </t>
   </si>
   <si>
-    <t>评估了多模态大模型GPT-4V在膳食评估领域的应用潜力，发现该模型在无需特定领域微调的情况下即可实现高达87.5%的食物识别准确率，并能通过语境感知利用周围物体作为比例参考进行份量估算（平均绝对误差54.6g）</t>
+    <t>评估了 GPT-4V（多模态 ChatGPT），解决了从单一食物图像中同时进行 食品检测、重量估算及多维度营养分析 的通用性与准确性验证问题</t>
+  </si>
+  <si>
+    <t>Investigating GPT Models for Nutritional Accuracy:A Systematic Review and Performance Enhancement</t>
+  </si>
+  <si>
+    <t>毕业论文</t>
+  </si>
+  <si>
+    <t>使用 GPT-3.5 Turbo 和 GPT-4 Turbo，结合 检索增强生成（RAG） 技术（集成 NutritionIX API），解决了大语言模型在生成 膳食计划 时 营养数据（如能量、蛋白质）不准确 的问题</t>
+  </si>
+  <si>
+    <t>Knowledge-Infused LLM-Powered Conversational Health Agent: A Case Study for Diabetes Patients</t>
+  </si>
+  <si>
+    <t>EMBC</t>
+  </si>
+  <si>
+    <t>该研究构建了一个 知识注入的对话健康智能体（CHA），利用 LLM（如 GPT-4） 集成外部数据库（Nutritionix）和指南（ADA），解决了通用LLM在 糖尿病饮食管理 中计算营养摄入时容易产生幻觉和不准确的问题</t>
   </si>
   <si>
     <t>Personalized Medicine in Urolithiasis: AI Chatbot-Assisted Dietary Management of Oxalate for Kidney Stone Prevention</t>
@@ -103,31 +148,13 @@
     <t>Journal of Personalized Medicine</t>
   </si>
   <si>
-    <t>评估了四种主流大模型（ChatGPT-3.5、ChatGPT-4、Bard AI和Bing Chat）在草酸盐膳食管理中的分类准确性，发现Bard AI以84%的总体准确率显著优于其他模型，而ChatGPT系列表现相对较差（52%和49%）</t>
-  </si>
-  <si>
-    <t>A Hybrid LLM based Model for Calorie Tracker and Dietary Control</t>
-  </si>
-  <si>
-    <t>ICEC</t>
-  </si>
-  <si>
-    <t>基于混合大语言模型（GPT-3/GPT-4）的卡路里追踪与饮食控制系统，通过集成文本描述、条形码扫描、图片识别与可穿戴设备数据，结合 LSTM/GRU 深度学习模块提供个性化营养建议与实时反馈，在 10-30 次测试中模型构建时间稳定在 1.3–3.2 秒、推理延迟低至 1.5 秒</t>
-  </si>
-  <si>
-    <t>Investigating GPT Models for Nutritional Accuracy:A Systematic Review and Performance Enhancement</t>
-  </si>
-  <si>
-    <t>毕业论文</t>
-  </si>
-  <si>
-    <t>针对 GPT 系列大模型的营养信息准确性系统研究，通过两阶段实验（首阶段评估 GPT-3.5/4 在 150 种食物上的营养估算误差，次阶段引入 NutritionIX API 的检索增强生成技术）将能量估算平均绝对误差降至 18.2 kcal（SMAPE 10.8%）</t>
+    <t>评估了 ChatGPT-3.5、ChatGPT-4、Bard AI 和 Bing Chat 等基于文本的聊天机器人，解决了针对肾结石预防的 食物草酸含量分类（低、中、高）的准确性问题</t>
   </si>
   <si>
     <t>RoDE: Linear Rectified Mixture of Diverse Experts for Food Large Multi-Modal Models</t>
   </si>
   <si>
-    <t>基于线性整流混合专家（RoDE）架构的食品大模型多任务优化框架，通过异构 LoRA 专家池（秩 2/4/6/8）与 ReLU 稀疏路由机制，在 Uni-Food 数据集上实现食材识别 IoU 26.86%（较基线提升 18.9%）、食谱生成 SacreBLEU 9.66（提升 11.2%）及营养估算 pMAE 52.58（降低 1.0%）的全面性能突破</t>
+    <t>提出了 RoDE（线性修正多样化专家混合） 架构，通过微调多模态模型（基于 LLaVA），解决了在单一模型中同时处理 营养估算、食谱生成和成分识别等多任务时的 数据冲突与参数效率 问题</t>
   </si>
   <si>
     <t>Advancing Food Nutrition Estimation via Visual-Ingredient Feature Fusion</t>
@@ -136,7 +163,7 @@
     <t>ICMR</t>
   </si>
   <si>
-    <t>提出了视觉-成分特征融合（VIF²）方法，通过整合大模型生成的成分信息与视觉特征来提升营养估计精度</t>
+    <t>提出了 Visual-Ingredient Feature Fusion (VIF²) 方法，利用 GPT-4o 进行半自动成分标注与测试时的预测修正，解决了因缺乏大规模营养标注数据（构建了 FastFood 数据集）而导致的 精准营养估算 困难问题</t>
   </si>
   <si>
     <t>An Evaluation of ChatGPT for Nutrient Content Estimation from Meal Photographs</t>
@@ -145,28 +172,89 @@
     <t>Nutrients</t>
   </si>
   <si>
-    <t>评估了ChatGPT-4基于餐食照片进行营养估计的能力，发现该大模型在食物识别方面表现优异（精确度93.0%），但在份量估计和营养含量计算上存在显著局限</t>
+    <t>评估了 ChatGPT-4 的多模态能力，解决了仅凭 餐食照片 进行食物识别、份量估算 以及 16种详细营养成分（如叶酸、钙等）测算的准确性验证问题</t>
+  </si>
+  <si>
+    <t>Are Vision-Language Models Ready for Dietary Assessment? Exploring the Next Frontier in AI-Powered Food Image Recognition</t>
+  </si>
+  <si>
+    <t>CVPRW</t>
+  </si>
+  <si>
+    <t>评估了 ChatGPT-4、Gemini、Claude 3、LLaVA 等6种视觉语言模型（VLM），解决了饮食评估前置步骤中的 细粒度食物识别（包括类别、子类别及烹饪方式判定）的准确性问题</t>
   </si>
   <si>
     <t>Comprehensive Evaluation of Large MultimodalModels for Nutrition Analysis: A New BenchmarkEnriched with Contextual Metadata</t>
   </si>
   <si>
-    <t>通过新构建的ACETADA数据集（包含806张经营养师验证的餐食图像及GPS坐标、时间戳等上下文元数据），首次对8种大型多模态模型（4种开源权重和4种闭源权重）在营养分析任务中的性能进行了全面评估</t>
-  </si>
-  <si>
-    <t>Decomposing Food Images for Better Nutrition Analysis: A Nutritionist-Inspired Two-Step Multimodal LLM Approach</t>
-  </si>
-  <si>
-    <t>CVPRW</t>
-  </si>
-  <si>
-    <t>受营养师工作流程启发的两步骤多模态大模型（MLLM）方法，通过将食物图像分析分解为成分识别（步骤一）和营养计算（步骤二）的序列化推理过程，显著提升了现成多模态大模型在营养估计任务中的准确性，无需额外微调即可实现更可靠的热量和宏量营养素预测</t>
+    <t>对比了 GPT-4o、Claude 3.5、Gemini 1.5 等8种LMM，通过整合 上下文元数据（GPS位置、时间戳） 到提示词中，解决了 卡路里与常量营养素估算 中因缺乏环境语境导致的幻觉和误差问题</t>
+  </si>
+  <si>
+    <t>Decomposing Food Images for Better Nutrition Analysis: A Nutritionist-Inspired
+Two-Step Multimodal LLM Approach</t>
+  </si>
+  <si>
+    <t>提出了一种模拟营养师思维的 两步提示法（Two-step Prompting），利用 Gemini 1.5 Pro、GPT-4o 等通用MLLM，解决了直接从图像估算 卡路里和宏量营养素 精度低的问题（通过先分析成分与份量，再计算营养）</t>
+  </si>
+  <si>
+    <t>DietAI24 as a framework forcomprehensive nutrition estimation usingmultimodal large language models</t>
+  </si>
+  <si>
+    <t>Communications Medicine</t>
+  </si>
+  <si>
+    <t>提出了 DietAI24 框架，结合 多模态LLM（GPT-4 Vision） 与 检索增强生成（RAG） 技术（索引FNDDS数据库），解决了传统方法难以从食物图像中零样本（Zero-shot）准确估算 65种全面营养成分（不仅仅是常量营养素）的问题</t>
   </si>
   <si>
     <t>DietGlance: Dietary Monitoring and Personalized Analysis at a Glance with Knowledge-Empowered AI Assistant</t>
   </si>
   <si>
-    <t>提出了DietGlance系统，通过智能眼镜实现自动化饮食监测，并利用检索增强生成（RAG）技术赋能大语言模型（GPT-4V）进行营养分析和个性化膳食建议，在自由生活场景下实现了高精度的食物识别（F1-score=0.972）和可靠的营养估算（热量MAPE=9.13%）</t>
+    <t>开发了 DietGlance 系统，利用智能眼镜捕获数据，通过 GPT-4V 结合 RAG（营养知识库），解决了在保护隐私的前提下自动检测进食行为、识别食物并提供 个性化营养分析与建议 的问题</t>
+  </si>
+  <si>
+    <t>FoodAgent: A Multi-modal Mixture of Experts Reasoning Agent for Divide-and-Conquer Food Nutrition Estimation</t>
+  </si>
+  <si>
+    <t>IEEE-EMBS</t>
+  </si>
+  <si>
+    <t>提出了 FoodAgent，采用 混合专家（MoE） 架构的推理智能体（基于 Qwen2.5），将食物成分动态路由至 单目体积估算器（MFP3D）、RAG 或 直接LLM推理 等不同模块，解决了 复杂混合菜肴 中不同成分难以通过单一模型精准估算营养的问题</t>
+  </si>
+  <si>
+    <t>FoodLMM: A Versatile Food Assistant using Large Multi-modal Model</t>
+  </si>
+  <si>
+    <t>IEEE Transactions on Multimedia</t>
+  </si>
+  <si>
+    <t>提出了 FoodLMM，基于 LISA/LLaVA 模型引入 任务专用Token（Task-specific Tokens） 和回归头进行多任务微调，解决了单一模型无法同时完成食物分割、食谱生成以及 精准营养数值回归（如卡路里、蛋白质质量）的问题</t>
+  </si>
+  <si>
+    <t>From bytes to bites: application of large language models to enhance nutritional recommendations</t>
+  </si>
+  <si>
+    <t>CKJ</t>
+  </si>
+  <si>
+    <t>评估了 ChatGPT (GPT-3.5/4) 等LLM在 慢性肾脏病（CKD） 营养管理中的应用，指出了其在生成食谱方面的潜力，但揭示了其在 微量营养素（如钾、磷）和卡路里估算 方面仍存在准确性不足的问题</t>
+  </si>
+  <si>
+    <t>KERL: Knowledge-Enhanced Personalized Recipe Recommendation using Large Language Models</t>
+  </si>
+  <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>提出了 KERL 系统，利用 知识图谱（FoodKG） 增强的 Phi-3-mini 模型（配合 Multi-LoRA 适配器），解决了在 个性化食谱推荐 过程中生成符合特定微量营养素约束（如低钠、低脂）的 营养信息 的问题</t>
+  </si>
+  <si>
+    <t>Large language models in clinical nutrition: an overview of its applications, capabilities, limitations, and potential future prospects</t>
+  </si>
+  <si>
+    <t>Frontiers in Nutrition</t>
+  </si>
+  <si>
+    <t>概述了 LLM（如ChatGPT） 结合 提示工程 和 微调 技术在临床营养中的应用，分析了其在 膳食计划制定、营养不良风险评估 及肥胖管理中的能力与局限性（如幻觉风险）</t>
   </si>
   <si>
     <t>Large Language Models in Nutritional Recognition: A Comprehensive Review of Applications</t>
@@ -175,13 +263,13 @@
     <t>International Conference on Computer and Communication Systems</t>
   </si>
   <si>
-    <t>综述了大语言模型（LLMs）在营养识别领域的应用进展，揭示了通过多模态融合、检索增强生成（RAG）和营养专用令牌等技术增强的LLMs能够显著提升膳食分析的准确性、可扩展性和个性化水平，但在数据集依赖性、计算效率和幻觉风险等方面仍面临重大挑战</t>
+    <t>系统回顾了 多模态LLM 在 营养识别 领域的应用，讨论了通过 营养专用Token化 和 视文对齐 技术解决传统深度学习方法在现实场景中适应性差和缺乏语义理解的问题</t>
   </si>
   <si>
     <t>LLMs for energy and macronutrients estimation using only text data from 24-hour dietary  recalls: a parameter-efficient fine-tuning experiment using a 10-shot prompt</t>
   </si>
   <si>
-    <t>通过参数高效微调（PEFT）实验证明，开源大语言模型（LLMs）仅基于24小时膳食回忆的纯文本数据即可实现能量和宏量营养素的准确估算，其中经过微调的模型将能量平均绝对误差（MAE）从基线652.08大幅降低至171.34-190.99，林氏一致性相关系数（Lin's CCC）从低于0.46提升至0.89以上，展现了文本驱动营养评估的可行性和高效性</t>
+    <t>使用 Mistral-Small-24B-Instruct-2501 (4-bit) 模型，结合 10-shot 思维链（CoT）提示 和 参数高效微调（PEFT/LoRA） 技术，解决了仅依据 24小时饮食回顾的文本描述（无图像）来估算能量及五种常量营养素（蛋白质、碳水化合物等）准确性低的问题</t>
   </si>
   <si>
     <t>NUTRIBENCH: A DATASET FOR EVALUATING LARGE LANGUAGE MODELS ON NUTRITION ESTIMATION FROM MEAL DESCRIPTIONS</t>
@@ -190,7 +278,16 @@
     <t>ICLR</t>
   </si>
   <si>
-    <t>提出了NUTRIBENCH——首个针对大语言模型（LLMs）基于纯文本膳食描述进行营养估算的公开基准数据集，通过系统评估12个主流LLMs在碳水化合物估算任务中的表现，发现GPT-4o结合思维链（CoT）提示以66.82%的准确率和99.16%的回答率实现最佳性能，其表现甚至超越专业营养师的速度和精度，证明了LLMs在无图像输入场景下实现精准营养评估的可行性</t>
+    <t>构建了基准数据集，评估了 GPT-4o、Llama 3.1、Gemma 2 等12种LLM，采用了 思维链（CoT） 和 检索增强生成（RAG） 策略，并微调了 Gemma2-27B，解决了基于 自然语言餐食描述 进行精准碳水化合物估算的问题</t>
+  </si>
+  <si>
+    <t>NutriGuard: LLM-Driven Nutritional Assessment for Chronic Disease Prevention</t>
+  </si>
+  <si>
+    <t>QPAIN</t>
+  </si>
+  <si>
+    <t>提出了一个名为 NutriGuard 的系统，利用微调后的 Llama-3.2 模型结合 OCR（PaddleOCR/Surya） 技术，解决了基于 食品标签 的个性化饮食风险评估（如针对糖尿病患者识别隐形糖分）及生成临床与文化适配的饮食建议的问题</t>
   </si>
   <si>
     <t>Performance Evaluation of 3 Large Language Models for Nutritional Content Estimation from Food Images</t>
@@ -199,100 +296,25 @@
     <t>Current Developments in Nutrition</t>
   </si>
   <si>
-    <t>评估三大主流多模态大语言模型（ChatGPT-4o、Claude 3.5 Sonnet和Gemini 1.5 Pro）在基于食物图像进行营养估算的性能，发现ChatGPT和Claude在重量和能量估算中达到36%左右的平均绝对百分比误差（MAPE），其精度已接近传统自我报告膳食评估方法的水平，而Gemini在所有营养素估算中均表现出显著更高的误差（MAPE 64.2%-109.9%），揭示了当前通用大模型在临床级精准营养评估中的局限性</t>
+    <t>对比评估了 ChatGPT-4o、Claude 3.5 Sonnet 和 Gemini 1.5 Pro 三种通用模型，使用 标准化提示词，解决了利用 食物图像 估算食物重量、能量和常量营养素时存在的系统性偏差（如大份量低估）问题</t>
+  </si>
+  <si>
+    <t>Prediction of Nutritional Content in Peruvian Lunch Meals by Large Language Models: A One-Shot Evaluation</t>
+  </si>
+  <si>
+    <t>使用 Gemma-3（4B, 12B, 27B） 模型，采用 单次提示（One-Shot Prompting） 技术，探索解决了基于 图像和文本描述 预测秘鲁午餐中能量及微量营养素（如铁、维生素A、锌）含量的问题（尽管目前精度尚不足以用于临床）</t>
   </si>
   <si>
     <t>Reasoning-Driven Food Energy Estimation via Multimodal Large Language Models</t>
   </si>
   <si>
-    <t>通过微调（fine-tuning）和体积注入（volume injection）两大创新策略，显著提升了多模态大语言模型（MLLMs）在基于图像的食物能量估算中的性能，其中经LoRA微调的LLaVA-1.5-13B模型在Nutrition5k数据集上实现了最低平均绝对误差（MAE=58.2 kcal），而体积注入技术使GPT-4o在零样本设置下的估算误差降低了21.8%，证明了MLLMs通过结合视觉推理与体积感知能力在膳食评估领域的巨大潜力</t>
-  </si>
-  <si>
-    <t>Are Vision-Language Models Ready for Dietary Assessment? Exploring the Next Frontier in AI-Powered Food Image Recognition</t>
-  </si>
-  <si>
-    <t>通过系统评估六种前沿视觉-语言模型（VLMs）在膳食评估任务中的表现，揭示了当前大模型在食物图像识别领域的优势与局限：闭源模型（Gemini、ChatGPT、Claude）在单一食物图像识别中专家加权召回率（EWR）超90%，但在细粒度烹饪风格识别上骤降至50%，凸显了其在复杂膳食场景中的推理瓶颈</t>
-  </si>
-  <si>
-    <t>FoodAgent: A Multi-modal Mixture of Experts Reasoning Agent for Divide-and-Conquer Food Nutrition Estimation</t>
-  </si>
-  <si>
-    <t>IEEE-EMBS</t>
-  </si>
-  <si>
-    <t>提出了FoodAgent——一个基于多模态专家混合（MoE）架构的智能推理系统，通过分而治之的策略显著提升了大模型在食物营养估计任务中的准确性，将传统整体式处理方法转化为针对不同食物成分的模块化专家路由机制</t>
-  </si>
-  <si>
-    <t>FoodLMM: A Versatile Food Assistant using Large Multi-modal Model</t>
-  </si>
-  <si>
-    <t>IEEE Transactions on Multimedia</t>
-  </si>
-  <si>
-    <t>FoodLMM基于LLaVA架构构建，引入了三类任务特定令牌：营养估计令牌（&lt;mass&gt;, &lt;cal&gt;, &lt;carb&gt;, &lt;fat&gt;, &lt;pro&gt;）、分割令牌（&lt;seg₁&gt;至&lt;segₙ&gt;）和对话令牌，使模型能够同时输出结构化数值（营养值）、分割掩码和自然语言响应</t>
-  </si>
-  <si>
-    <t>Large language models in clinical nutrition: an overview of its applications, capabilities, limitations, and potential future prospects</t>
-  </si>
-  <si>
-    <t>Frontiers in Nutrition</t>
-  </si>
-  <si>
-    <t>在营养成分量化分析中，ChatGPT-4对能量的估算误差为36%，蛋白质28%，钾49%，磷54%，凸显其在精确营养计算中的系统性偏差</t>
-  </si>
-  <si>
-    <t>Prediction of Nutritional Content in Peruvian Lunch Meals by Large Language Models: A One-Shot Evaluation</t>
-  </si>
-  <si>
-    <t>针对秘鲁午餐营养评估的大模型性能研究，通过单样本提示策略测试 Gemma-3 系列模型（4B/12B/27B）对 510 道传统餐食的能量与微量营养素预测能力，发现 27B 模型在热量（MAE 108 kcal）、碳水化合物（MAE 26 g）及锌（MAE 1 mg）估算中误差最低，而 12B 模型在蛋白质预测上达成 70% 临床误差阈值符合率，揭示当前通用大模型在区域特色膳食营养量化任务中仍存在显著精度局限（平均符合率＜45%）</t>
-  </si>
-  <si>
-    <t>Artificial intelligence chatbots for the nutrition management of diabetes and the metabolic syndrome</t>
-  </si>
-  <si>
-    <t>EJCN</t>
-  </si>
-  <si>
-    <t>针对 ChatGPT（GPT-3.5-turbo）在糖尿病与代谢综合征营养管理中的性能评估研究，通过 63 个提示词系统测试其膳食干预、营养诊疗流程（NCP）及 1500 kcal 日菜单规划三大领域的输出准确性，发现尽管生成内容清晰度获评良好至优秀（3-4 分 Likert 量表），但在能量赤字建议（缺失率 100%）、体重管理（缺失率 85%）、微量营养素量化（钙与维生素 D 摄入量严重偏离推荐值）</t>
-  </si>
-  <si>
-    <t>Comparison of the Accuracy, Completeness, Reproducibility,and Consistency of Different AI Chatbots in ProvidingNutritional Advice: An Exploratory Study</t>
-  </si>
-  <si>
-    <t>JCM</t>
-  </si>
-  <si>
-    <t>针对 10 种通用大模型聊天机器人（含 ChatGPT-3.5/4.0、Gemini、Copilot 等）营养建议性能的探索性研究，通过连续三日提交肥胖无并发症（Case 1）及肥胖合并糖尿病、 sarcopenia 与慢性肾病（Case 2）的临床案例提示词，并由注册营养师从准确性、完整性、可复现性及一致性四维度评估输出结果，发现 ChatGPT-3.5 在基础案例中准确性最高（67.2%），但在复杂案例中所有模型均未达 50% 准确率，且普遍存在蛋白质建议自相矛盾（如同时推荐“增蛋白”与“限蛋白”）、能量计算偏差（最高达 55%）、及三日回答可复现率低下（ChatGPT-4.0 仅 50%）等严重缺陷</t>
-  </si>
-  <si>
-    <t>Knowledge-Infused LLM-Powered Conversational Health Agent: A Case Study for Diabetes Patients</t>
-  </si>
-  <si>
-    <t>EMBC</t>
-  </si>
-  <si>
-    <t>基于知识增强大语言模型（LLM）的对话健康代理（CHA），通过整合美国糖尿病协会（ADA）膳食指南与 Nutritionix 营养数据库，并嵌入营养摄入计算与风险评估分析工具，显著提升了对糖尿病患者日常饮食管理的精准性——在 100 例糖尿病相关膳食咨询测试中，其风险营养素（如碳水化合物、脂肪、蛋白质等）评估准确率全面超越 GPT-4（平均提升 35.7%），尤其在饱和脂肪（99% vs 68%）和蛋白质（90% vs 17%）判定上展现出色性能</t>
-  </si>
-  <si>
-    <t>From bytes to bites: application of large language models to enhance nutritional recommendations</t>
-  </si>
-  <si>
-    <t>CKJ</t>
-  </si>
-  <si>
-    <t>评估了大语言模型（LLMs）在慢性肾脏病（CKD）营养管理中的应用潜力与局限，指出当前模型（如 ChatGPT-4）在食谱生成与多语言翻译（Likert 评分 4/5）方面表现良好，但营养估算存在严重偏差：能量低估 36%、蛋白质低估 28%、电解质（钾、磷、钠）低估 49–54%，且图像识别辅助工具仅能识别 85% 可见成分</t>
-  </si>
-  <si>
-    <t>KERL: Knowledge-Enhanced Personalized Recipe Recommendation using Large Language Models</t>
-  </si>
-  <si>
-    <t>ACL</t>
-  </si>
-  <si>
-    <t>KERL——一种基于多 LoRA 适配器架构的知识增强大语言模型系统，通过整合 FoodKG（含 100 万食谱与 6700 万三元组）实现个性化食物推荐、食谱生成与营养分析的三元任务协同，其核心创新在于采用任务特异性 LoRA 微调（Phi-3-mini 为基础模型）与知识图谱子图检索增强技术，在自建的大规模基准测试（含 77,900 条约束性问答对）中显著超越基线模型：推荐模块 F1 达 85.4%（较 LLaMA-2 提升 56.5%），食谱生成 BLEU-4 提升至 0.347（较基准提升 20%），营养估算 MAE 降低 50%</t>
-  </si>
-  <si>
-    <t>构建 FoodNExTDB 专家标注食物图像数据库（含 9,263 张图像、50,000 个营养标签）系统评估六种前沿视觉-语言模型（VLMs），揭示闭源模型（Gemini/94.5% EWR、ChatGPT/90.7% EWR）在单产品图像识别中显著优于开源模型，但所有模型在细粒度烹饪风格识别上表现严重受限（最佳仅 50% EWR）</t>
+    <t>提出了一种基于 LLaVA-1.5 的多模态LLM，结合 LoRA 微调 和 体积注入（Volume Injection） 方法（集成 Grounding DINO、SAM 和 Marigold 工具），解决了基于图像的卡路里估算中因 体积识别 不准导致误差的问题</t>
+  </si>
+  <si>
+    <t>A Closed-Loop Multi-Agent System Driven by LLMs for Meal-Level Personalized Nutrition Management</t>
+  </si>
+  <si>
+    <t>构建了一个由 GPT-4o（视觉）、Claude Sonnet（文件管理）、GPT-4o-mini（控制与对话） 驱动的多智能体系统（Multi-Agent System），解决了 膳食级 的个性化营养管理闭环问题（包括从照片估算营养、更新每日预算到动态推荐下一餐）</t>
   </si>
 </sst>
 </file>
@@ -936,7 +958,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -960,6 +982,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1272,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="165.272727272727" style="1" customWidth="1"/>
@@ -1414,7 +1439,7 @@
       <c r="B10" s="2">
         <v>2024</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D10" t="s">
@@ -1428,310 +1453,339 @@
       <c r="B11" s="2">
         <v>2024</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
+      <c r="C11" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2">
         <v>2025</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2">
         <v>2025</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2">
         <v>2025</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2">
         <v>2025</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
         <v>2025</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
-        <v>54</v>
+      <c r="A20" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="B20" s="2">
         <v>2025</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2">
         <v>2025</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2">
         <v>2025</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2">
         <v>2025</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2">
         <v>2025</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2">
         <v>2025</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2">
         <v>2025</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B27" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2">
         <v>2025</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B31" s="2">
         <v>2025</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="5" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2">
         <v>2025</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D27">
-    <sortCondition ref="B2"/>
+  <sortState ref="A2:D35">
+    <sortCondition ref="B2:B35"/>
+    <sortCondition ref="A2:A35"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
